--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEVADA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEVADA_2022.xlsx
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C152">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C258">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C265">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C677">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C748">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C781">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C786">
